--- a/artfynd/A 9162-2024 artfynd.xlsx
+++ b/artfynd/A 9162-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118913017</v>
+        <v>118912076</v>
       </c>
       <c r="B2" t="n">
-        <v>78484</v>
+        <v>90469</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,29 +687,33 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -718,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>802714</v>
+        <v>802588</v>
       </c>
       <c r="R2" t="n">
-        <v>7146151</v>
+        <v>7146291</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,22 +773,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118911374</v>
+        <v>118911959</v>
       </c>
       <c r="B3" t="n">
-        <v>78484</v>
+        <v>97846</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +797,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -831,7 +840,7 @@
         <v>802668</v>
       </c>
       <c r="R3" t="n">
-        <v>7146310</v>
+        <v>7146187</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,6 +873,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>15 st i blomning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118911445</v>
+        <v>118912793</v>
       </c>
       <c r="B4" t="n">
         <v>57290</v>
@@ -939,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>802707</v>
+        <v>802713</v>
       </c>
       <c r="R4" t="n">
-        <v>7146299</v>
+        <v>7146294</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +993,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>äldre påbörjat bohål i gran</t>
+          <t>Påbörjat bohål</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,22 +1008,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118911463</v>
+        <v>118911374</v>
       </c>
       <c r="B5" t="n">
-        <v>90469</v>
+        <v>78484</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,31 +1032,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1053,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>802822</v>
+        <v>802668</v>
       </c>
       <c r="R5" t="n">
-        <v>7146243</v>
+        <v>7146310</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1226,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118911433</v>
+        <v>118912901</v>
       </c>
       <c r="B7" t="n">
-        <v>78518</v>
+        <v>78484</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,29 +1256,25 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1273,10 +1283,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>802684</v>
+        <v>802814</v>
       </c>
       <c r="R7" t="n">
-        <v>7146303</v>
+        <v>7146177</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,22 +1334,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118912802</v>
+        <v>118911445</v>
       </c>
       <c r="B8" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,26 +1362,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1379,10 +1394,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>802711</v>
+        <v>802707</v>
       </c>
       <c r="R8" t="n">
-        <v>7146289</v>
+        <v>7146299</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,35 +1432,39 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>äldre påbörjat bohål i gran</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118912851</v>
+        <v>118911495</v>
       </c>
       <c r="B9" t="n">
-        <v>78484</v>
+        <v>82263</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1458,30 +1477,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1489,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>802826</v>
+        <v>802848</v>
       </c>
       <c r="R9" t="n">
-        <v>7146174</v>
+        <v>7146203</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,22 +1559,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118913527</v>
+        <v>118912755</v>
       </c>
       <c r="B10" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1568,31 +1587,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1600,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>802655</v>
+        <v>802684</v>
       </c>
       <c r="R10" t="n">
-        <v>7146316</v>
+        <v>7146282</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1644,6 +1658,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1662,10 +1677,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118913502</v>
+        <v>118913094</v>
       </c>
       <c r="B11" t="n">
-        <v>90847</v>
+        <v>78484</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1674,25 +1689,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1705,10 +1720,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>802579</v>
+        <v>802616</v>
       </c>
       <c r="R11" t="n">
-        <v>7146294</v>
+        <v>7146197</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1768,10 +1783,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118913425</v>
+        <v>118913017</v>
       </c>
       <c r="B12" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1784,31 +1799,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1816,10 +1826,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>802623</v>
+        <v>802714</v>
       </c>
       <c r="R12" t="n">
-        <v>7146248</v>
+        <v>7146151</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1860,6 +1870,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1878,10 +1889,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118913094</v>
+        <v>118911768</v>
       </c>
       <c r="B13" t="n">
-        <v>78484</v>
+        <v>97846</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1890,30 +1901,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1921,10 +1937,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>802616</v>
+        <v>802693</v>
       </c>
       <c r="R13" t="n">
-        <v>7146197</v>
+        <v>7146165</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1972,22 +1988,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118912837</v>
+        <v>118911573</v>
       </c>
       <c r="B14" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1996,35 +2012,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2032,10 +2052,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>802834</v>
+        <v>802695</v>
       </c>
       <c r="R14" t="n">
-        <v>7146213</v>
+        <v>7146163</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2070,34 +2090,40 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ca 60st i blomning</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118913543</v>
+        <v>118913502</v>
       </c>
       <c r="B15" t="n">
-        <v>78484</v>
+        <v>90847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2106,25 +2132,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2137,10 +2163,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>802655</v>
+        <v>802579</v>
       </c>
       <c r="R15" t="n">
-        <v>7146316</v>
+        <v>7146294</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2200,10 +2226,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118911573</v>
+        <v>118912837</v>
       </c>
       <c r="B16" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2212,39 +2238,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2252,10 +2274,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>802695</v>
+        <v>802834</v>
       </c>
       <c r="R16" t="n">
-        <v>7146163</v>
+        <v>7146213</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2290,40 +2312,34 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>ca 60st i blomning</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118912901</v>
+        <v>118912823</v>
       </c>
       <c r="B17" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2336,26 +2352,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2363,10 +2384,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>802814</v>
+        <v>802776</v>
       </c>
       <c r="R17" t="n">
-        <v>7146177</v>
+        <v>7146250</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2407,7 +2428,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2426,10 +2446,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118912076</v>
+        <v>118913436</v>
       </c>
       <c r="B18" t="n">
-        <v>90469</v>
+        <v>57290</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2438,34 +2458,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2473,10 +2494,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>802588</v>
+        <v>802622</v>
       </c>
       <c r="R18" t="n">
-        <v>7146291</v>
+        <v>7146257</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2517,29 +2538,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118911768</v>
+        <v>118913425</v>
       </c>
       <c r="B19" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2548,35 +2568,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2584,10 +2604,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>802693</v>
+        <v>802623</v>
       </c>
       <c r="R19" t="n">
-        <v>7146165</v>
+        <v>7146248</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2628,19 +2648,18 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2762,10 +2781,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118911959</v>
+        <v>118912775</v>
       </c>
       <c r="B21" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2774,39 +2793,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2814,10 +2829,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>802668</v>
+        <v>802682</v>
       </c>
       <c r="R21" t="n">
-        <v>7146187</v>
+        <v>7146278</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2852,40 +2867,34 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>15 st i blomning</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118911495</v>
+        <v>118911433</v>
       </c>
       <c r="B22" t="n">
-        <v>82263</v>
+        <v>78518</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2898,27 +2907,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -2929,10 +2938,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>802848</v>
+        <v>802684</v>
       </c>
       <c r="R22" t="n">
-        <v>7146203</v>
+        <v>7146303</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2992,10 +3001,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118913104</v>
+        <v>118912764</v>
       </c>
       <c r="B23" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3008,26 +3017,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3035,10 +3049,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>802635</v>
+        <v>802684</v>
       </c>
       <c r="R23" t="n">
-        <v>7146237</v>
+        <v>7146282</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3079,7 +3093,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3098,10 +3111,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118913472</v>
+        <v>118911985</v>
       </c>
       <c r="B24" t="n">
-        <v>90522</v>
+        <v>90469</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3110,29 +3123,33 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -3141,10 +3158,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>802619</v>
+        <v>802668</v>
       </c>
       <c r="R24" t="n">
-        <v>7146280</v>
+        <v>7146192</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3192,19 +3209,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118912755</v>
+        <v>118912802</v>
       </c>
       <c r="B25" t="n">
         <v>78484</v>
@@ -3247,10 +3264,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>802684</v>
+        <v>802711</v>
       </c>
       <c r="R25" t="n">
-        <v>7146282</v>
+        <v>7146289</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3310,7 +3327,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118912823</v>
+        <v>118913093</v>
       </c>
       <c r="B26" t="n">
         <v>57290</v>
@@ -3358,10 +3375,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>802776</v>
+        <v>802616</v>
       </c>
       <c r="R26" t="n">
-        <v>7146250</v>
+        <v>7146197</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3394,6 +3411,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3420,7 +3442,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118912775</v>
+        <v>118913527</v>
       </c>
       <c r="B27" t="n">
         <v>57290</v>
@@ -3468,10 +3490,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>802682</v>
+        <v>802655</v>
       </c>
       <c r="R27" t="n">
-        <v>7146278</v>
+        <v>7146316</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3530,10 +3552,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118912793</v>
+        <v>118913543</v>
       </c>
       <c r="B28" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3546,31 +3568,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3578,10 +3595,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>802713</v>
+        <v>802655</v>
       </c>
       <c r="R28" t="n">
-        <v>7146294</v>
+        <v>7146316</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3616,17 +3633,13 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Påbörjat bohål</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3645,10 +3658,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118913436</v>
+        <v>118913514</v>
       </c>
       <c r="B29" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3661,31 +3674,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3693,10 +3701,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>802622</v>
+        <v>802618</v>
       </c>
       <c r="R29" t="n">
-        <v>7146257</v>
+        <v>7146315</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3737,6 +3745,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3755,10 +3764,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118911854</v>
+        <v>118912851</v>
       </c>
       <c r="B30" t="n">
-        <v>97846</v>
+        <v>78484</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3767,35 +3776,34 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3803,10 +3811,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>802680</v>
+        <v>802826</v>
       </c>
       <c r="R30" t="n">
-        <v>7146179</v>
+        <v>7146174</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3854,22 +3862,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118912764</v>
+        <v>118911463</v>
       </c>
       <c r="B31" t="n">
-        <v>57290</v>
+        <v>90469</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3878,35 +3886,34 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3914,10 +3921,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>802684</v>
+        <v>802822</v>
       </c>
       <c r="R31" t="n">
-        <v>7146282</v>
+        <v>7146243</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3958,28 +3965,29 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118912875</v>
+        <v>118911854</v>
       </c>
       <c r="B32" t="n">
-        <v>78484</v>
+        <v>97846</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3988,30 +3996,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4019,10 +4032,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>802745</v>
+        <v>802680</v>
       </c>
       <c r="R32" t="n">
-        <v>7146191</v>
+        <v>7146179</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4070,22 +4083,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118912814</v>
+        <v>118912743</v>
       </c>
       <c r="B33" t="n">
-        <v>78484</v>
+        <v>91405</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4098,30 +4111,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>4745</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4129,10 +4138,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>802750</v>
+        <v>802703</v>
       </c>
       <c r="R33" t="n">
-        <v>7146284</v>
+        <v>7146394</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4192,10 +4201,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118912743</v>
+        <v>118912814</v>
       </c>
       <c r="B34" t="n">
-        <v>91405</v>
+        <v>78484</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4208,26 +4217,30 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4745</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4235,10 +4248,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>802703</v>
+        <v>802750</v>
       </c>
       <c r="R34" t="n">
-        <v>7146394</v>
+        <v>7146284</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4298,10 +4311,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118912023</v>
+        <v>118913472</v>
       </c>
       <c r="B35" t="n">
-        <v>82263</v>
+        <v>90522</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4314,29 +4327,25 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
@@ -4345,10 +4354,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>802582</v>
+        <v>802619</v>
       </c>
       <c r="R35" t="n">
-        <v>7146293</v>
+        <v>7146280</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4396,22 +4405,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118911985</v>
+        <v>118912023</v>
       </c>
       <c r="B36" t="n">
-        <v>90469</v>
+        <v>82263</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4420,25 +4429,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4455,10 +4464,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>802668</v>
+        <v>802582</v>
       </c>
       <c r="R36" t="n">
-        <v>7146192</v>
+        <v>7146293</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4518,10 +4527,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118913093</v>
+        <v>118912875</v>
       </c>
       <c r="B37" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4534,31 +4543,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4566,10 +4570,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>802616</v>
+        <v>802745</v>
       </c>
       <c r="R37" t="n">
-        <v>7146197</v>
+        <v>7146191</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4604,17 +4608,13 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4633,7 +4633,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118913514</v>
+        <v>118913104</v>
       </c>
       <c r="B38" t="n">
         <v>78484</v>
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>802618</v>
+        <v>802635</v>
       </c>
       <c r="R38" t="n">
-        <v>7146315</v>
+        <v>7146237</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 9162-2024 artfynd.xlsx
+++ b/artfynd/A 9162-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118912076</v>
+        <v>118913543</v>
       </c>
       <c r="B2" t="n">
-        <v>90469</v>
+        <v>78491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,33 +687,29 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -722,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>802588</v>
+        <v>802655</v>
       </c>
       <c r="R2" t="n">
-        <v>7146291</v>
+        <v>7146316</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -773,22 +769,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118911959</v>
+        <v>118912802</v>
       </c>
       <c r="B3" t="n">
-        <v>97846</v>
+        <v>78491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,39 +793,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>802668</v>
+        <v>802711</v>
       </c>
       <c r="R3" t="n">
-        <v>7146187</v>
+        <v>7146289</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,11 +862,6 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>15 st i blomning</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -893,22 +875,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118912793</v>
+        <v>118911959</v>
       </c>
       <c r="B4" t="n">
-        <v>57290</v>
+        <v>97853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,35 +899,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -953,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>802713</v>
+        <v>802668</v>
       </c>
       <c r="R4" t="n">
-        <v>7146294</v>
+        <v>7146187</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +979,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Påbörjat bohål</t>
+          <t>15 st i blomning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,28 +988,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118911374</v>
+        <v>118912775</v>
       </c>
       <c r="B5" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,30 +1023,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1067,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>802668</v>
+        <v>802682</v>
       </c>
       <c r="R5" t="n">
-        <v>7146310</v>
+        <v>7146278</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,19 +1099,18 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1133,7 +1120,7 @@
         <v>118912069</v>
       </c>
       <c r="B6" t="n">
-        <v>90504</v>
+        <v>90511</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1240,10 +1227,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118912901</v>
+        <v>118912814</v>
       </c>
       <c r="B7" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,7 +1262,11 @@
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1283,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>802814</v>
+        <v>802750</v>
       </c>
       <c r="R7" t="n">
-        <v>7146177</v>
+        <v>7146284</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1346,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118911445</v>
+        <v>118911374</v>
       </c>
       <c r="B8" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1362,31 +1353,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1394,10 +1384,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>802707</v>
+        <v>802668</v>
       </c>
       <c r="R8" t="n">
-        <v>7146299</v>
+        <v>7146310</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,17 +1422,13 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>äldre påbörjat bohål i gran</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1461,10 +1447,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118911495</v>
+        <v>118911854</v>
       </c>
       <c r="B9" t="n">
-        <v>82263</v>
+        <v>97853</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1473,34 +1459,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1508,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>802848</v>
+        <v>802680</v>
       </c>
       <c r="R9" t="n">
-        <v>7146203</v>
+        <v>7146179</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,10 +1558,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118912755</v>
+        <v>118913472</v>
       </c>
       <c r="B10" t="n">
-        <v>78484</v>
+        <v>90529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1574,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1614,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>802684</v>
+        <v>802619</v>
       </c>
       <c r="R10" t="n">
-        <v>7146282</v>
+        <v>7146280</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118913094</v>
+        <v>118912764</v>
       </c>
       <c r="B11" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1693,26 +1680,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1720,10 +1712,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>802616</v>
+        <v>802684</v>
       </c>
       <c r="R11" t="n">
-        <v>7146197</v>
+        <v>7146282</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1764,7 +1756,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1783,10 +1774,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118913017</v>
+        <v>118913425</v>
       </c>
       <c r="B12" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1799,26 +1790,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1826,10 +1822,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>802714</v>
+        <v>802623</v>
       </c>
       <c r="R12" t="n">
-        <v>7146151</v>
+        <v>7146248</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1870,7 +1866,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1889,10 +1884,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118911768</v>
+        <v>118911445</v>
       </c>
       <c r="B13" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1901,35 +1896,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1937,10 +1932,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>802693</v>
+        <v>802707</v>
       </c>
       <c r="R13" t="n">
-        <v>7146165</v>
+        <v>7146299</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1975,13 +1970,17 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>äldre påbörjat bohål i gran</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2000,10 +1999,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118911573</v>
+        <v>118913094</v>
       </c>
       <c r="B14" t="n">
-        <v>97846</v>
+        <v>78491</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2012,39 +2011,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2052,10 +2042,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>802695</v>
+        <v>802616</v>
       </c>
       <c r="R14" t="n">
-        <v>7146163</v>
+        <v>7146197</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2090,11 +2080,6 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>ca 60st i blomning</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2108,22 +2093,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118913502</v>
+        <v>118911927</v>
       </c>
       <c r="B15" t="n">
-        <v>90847</v>
+        <v>57306</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2132,30 +2117,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2062</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2163,10 +2153,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>802579</v>
+        <v>802674</v>
       </c>
       <c r="R15" t="n">
-        <v>7146294</v>
+        <v>7146180</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2201,35 +2191,39 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>hack i död gran</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118912837</v>
+        <v>118913514</v>
       </c>
       <c r="B16" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2242,31 +2236,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2274,10 +2263,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>802834</v>
+        <v>802618</v>
       </c>
       <c r="R16" t="n">
-        <v>7146213</v>
+        <v>7146315</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2318,6 +2307,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2446,10 +2436,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118913436</v>
+        <v>118911573</v>
       </c>
       <c r="B18" t="n">
-        <v>57290</v>
+        <v>97853</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2458,35 +2448,39 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2494,10 +2488,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>802622</v>
+        <v>802695</v>
       </c>
       <c r="R18" t="n">
-        <v>7146257</v>
+        <v>7146163</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2532,34 +2526,40 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>ca 60st i blomning</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118913425</v>
+        <v>118911768</v>
       </c>
       <c r="B19" t="n">
-        <v>57290</v>
+        <v>97853</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2568,35 +2568,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>802623</v>
+        <v>802693</v>
       </c>
       <c r="R19" t="n">
-        <v>7146248</v>
+        <v>7146165</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2648,28 +2648,29 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118911927</v>
+        <v>118912755</v>
       </c>
       <c r="B20" t="n">
-        <v>57306</v>
+        <v>78491</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2682,31 +2683,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2714,10 +2710,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>802674</v>
+        <v>802684</v>
       </c>
       <c r="R20" t="n">
-        <v>7146180</v>
+        <v>7146282</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2752,39 +2748,35 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>hack i död gran</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118912775</v>
+        <v>118912851</v>
       </c>
       <c r="B21" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2797,29 +2789,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2829,10 +2820,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>802682</v>
+        <v>802826</v>
       </c>
       <c r="R21" t="n">
-        <v>7146278</v>
+        <v>7146174</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2873,6 +2864,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2891,10 +2883,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118911433</v>
+        <v>118913502</v>
       </c>
       <c r="B22" t="n">
-        <v>78518</v>
+        <v>90854</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2903,33 +2895,29 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>2062</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -2938,10 +2926,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>802684</v>
+        <v>802579</v>
       </c>
       <c r="R22" t="n">
-        <v>7146303</v>
+        <v>7146294</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2989,19 +2977,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118912764</v>
+        <v>118913527</v>
       </c>
       <c r="B23" t="n">
         <v>57290</v>
@@ -3049,10 +3037,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>802684</v>
+        <v>802655</v>
       </c>
       <c r="R23" t="n">
-        <v>7146282</v>
+        <v>7146316</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3114,7 +3102,7 @@
         <v>118911985</v>
       </c>
       <c r="B24" t="n">
-        <v>90469</v>
+        <v>90476</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3221,10 +3209,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118912802</v>
+        <v>118912837</v>
       </c>
       <c r="B25" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3237,26 +3225,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3264,10 +3257,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>802711</v>
+        <v>802834</v>
       </c>
       <c r="R25" t="n">
-        <v>7146289</v>
+        <v>7146213</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3308,7 +3301,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3327,10 +3319,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118913093</v>
+        <v>118912076</v>
       </c>
       <c r="B26" t="n">
-        <v>57290</v>
+        <v>90476</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3339,35 +3331,34 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3375,10 +3366,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>802616</v>
+        <v>802588</v>
       </c>
       <c r="R26" t="n">
-        <v>7146197</v>
+        <v>7146291</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3413,39 +3404,35 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118913527</v>
+        <v>118913017</v>
       </c>
       <c r="B27" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3458,31 +3445,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3490,10 +3472,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>802655</v>
+        <v>802714</v>
       </c>
       <c r="R27" t="n">
-        <v>7146316</v>
+        <v>7146151</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3534,6 +3516,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3552,10 +3535,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118913543</v>
+        <v>118912793</v>
       </c>
       <c r="B28" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3568,26 +3551,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3595,10 +3583,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>802655</v>
+        <v>802713</v>
       </c>
       <c r="R28" t="n">
-        <v>7146316</v>
+        <v>7146294</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3633,13 +3621,17 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Påbörjat bohål</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3658,10 +3650,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118913514</v>
+        <v>118911433</v>
       </c>
       <c r="B29" t="n">
-        <v>78484</v>
+        <v>78525</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3674,25 +3666,29 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
@@ -3701,10 +3697,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>802618</v>
+        <v>802684</v>
       </c>
       <c r="R29" t="n">
-        <v>7146315</v>
+        <v>7146303</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3752,22 +3748,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118912851</v>
+        <v>118912023</v>
       </c>
       <c r="B30" t="n">
-        <v>78484</v>
+        <v>82270</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3780,30 +3776,30 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3811,10 +3807,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>802826</v>
+        <v>802582</v>
       </c>
       <c r="R30" t="n">
-        <v>7146174</v>
+        <v>7146293</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3862,22 +3858,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118911463</v>
+        <v>118911495</v>
       </c>
       <c r="B31" t="n">
-        <v>90469</v>
+        <v>82270</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3886,25 +3882,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3921,10 +3917,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>802822</v>
+        <v>802848</v>
       </c>
       <c r="R31" t="n">
-        <v>7146243</v>
+        <v>7146203</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3984,10 +3980,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118911854</v>
+        <v>118913104</v>
       </c>
       <c r="B32" t="n">
-        <v>97846</v>
+        <v>78491</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3996,35 +3992,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4032,10 +4023,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>802680</v>
+        <v>802635</v>
       </c>
       <c r="R32" t="n">
-        <v>7146179</v>
+        <v>7146237</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4083,22 +4074,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118912743</v>
+        <v>118911463</v>
       </c>
       <c r="B33" t="n">
-        <v>91405</v>
+        <v>90476</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4107,29 +4098,33 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4745</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
@@ -4138,10 +4133,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>802703</v>
+        <v>802822</v>
       </c>
       <c r="R33" t="n">
-        <v>7146394</v>
+        <v>7146243</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4189,22 +4184,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118912814</v>
+        <v>118912875</v>
       </c>
       <c r="B34" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4236,11 +4231,7 @@
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4248,10 +4239,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>802750</v>
+        <v>802745</v>
       </c>
       <c r="R34" t="n">
-        <v>7146284</v>
+        <v>7146191</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4311,10 +4302,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118913472</v>
+        <v>118913093</v>
       </c>
       <c r="B35" t="n">
-        <v>90522</v>
+        <v>57290</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4327,26 +4318,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4354,10 +4350,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>802619</v>
+        <v>802616</v>
       </c>
       <c r="R35" t="n">
-        <v>7146280</v>
+        <v>7146197</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4392,13 +4388,17 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4417,10 +4417,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118912023</v>
+        <v>118912901</v>
       </c>
       <c r="B36" t="n">
-        <v>82263</v>
+        <v>78491</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4433,29 +4433,25 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
@@ -4464,10 +4460,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>802582</v>
+        <v>802814</v>
       </c>
       <c r="R36" t="n">
-        <v>7146293</v>
+        <v>7146177</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4515,22 +4511,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118912875</v>
+        <v>118912743</v>
       </c>
       <c r="B37" t="n">
-        <v>78484</v>
+        <v>91412</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4543,21 +4539,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>4745</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4570,10 +4566,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>802745</v>
+        <v>802703</v>
       </c>
       <c r="R37" t="n">
-        <v>7146191</v>
+        <v>7146394</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4633,10 +4629,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118913104</v>
+        <v>118913436</v>
       </c>
       <c r="B38" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4649,26 +4645,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4676,10 +4677,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>802635</v>
+        <v>802622</v>
       </c>
       <c r="R38" t="n">
-        <v>7146237</v>
+        <v>7146257</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4720,7 +4721,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9162-2024 artfynd.xlsx
+++ b/artfynd/A 9162-2024 artfynd.xlsx
@@ -1774,10 +1774,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118913425</v>
+        <v>118913094</v>
       </c>
       <c r="B12" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1790,31 +1790,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1822,10 +1817,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>802623</v>
+        <v>802616</v>
       </c>
       <c r="R12" t="n">
-        <v>7146248</v>
+        <v>7146197</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1866,6 +1861,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1884,7 +1880,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118911445</v>
+        <v>118913425</v>
       </c>
       <c r="B13" t="n">
         <v>57290</v>
@@ -1932,10 +1928,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>802707</v>
+        <v>802623</v>
       </c>
       <c r="R13" t="n">
-        <v>7146299</v>
+        <v>7146248</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1970,11 +1966,6 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>äldre påbörjat bohål i gran</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1987,22 +1978,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118913094</v>
+        <v>118911445</v>
       </c>
       <c r="B14" t="n">
-        <v>78491</v>
+        <v>57290</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2015,26 +2006,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2042,10 +2038,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>802616</v>
+        <v>802707</v>
       </c>
       <c r="R14" t="n">
-        <v>7146197</v>
+        <v>7146299</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2080,25 +2076,29 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>äldre påbörjat bohål i gran</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2989,10 +2989,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118913527</v>
+        <v>118911985</v>
       </c>
       <c r="B23" t="n">
-        <v>57290</v>
+        <v>90476</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3001,35 +3001,34 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3037,10 +3036,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>802655</v>
+        <v>802668</v>
       </c>
       <c r="R23" t="n">
-        <v>7146316</v>
+        <v>7146192</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3081,28 +3080,29 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118911985</v>
+        <v>118913527</v>
       </c>
       <c r="B24" t="n">
-        <v>90476</v>
+        <v>57290</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3111,34 +3111,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3146,10 +3147,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>802668</v>
+        <v>802655</v>
       </c>
       <c r="R24" t="n">
-        <v>7146192</v>
+        <v>7146316</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3190,29 +3191,28 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118912837</v>
+        <v>118913017</v>
       </c>
       <c r="B25" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3225,31 +3225,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3257,10 +3252,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>802834</v>
+        <v>802714</v>
       </c>
       <c r="R25" t="n">
-        <v>7146213</v>
+        <v>7146151</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3301,6 +3296,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3429,10 +3425,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118913017</v>
+        <v>118912837</v>
       </c>
       <c r="B27" t="n">
-        <v>78491</v>
+        <v>57290</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3445,26 +3441,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3472,10 +3473,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>802714</v>
+        <v>802834</v>
       </c>
       <c r="R27" t="n">
-        <v>7146151</v>
+        <v>7146213</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3516,7 +3517,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9162-2024 artfynd.xlsx
+++ b/artfynd/A 9162-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118913543</v>
+        <v>118912755</v>
       </c>
       <c r="B2" t="n">
         <v>78491</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>802655</v>
+        <v>802684</v>
       </c>
       <c r="R2" t="n">
-        <v>7146316</v>
+        <v>7146282</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118912802</v>
+        <v>118913472</v>
       </c>
       <c r="B3" t="n">
-        <v>78491</v>
+        <v>90529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>802711</v>
+        <v>802619</v>
       </c>
       <c r="R3" t="n">
-        <v>7146289</v>
+        <v>7146280</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118911959</v>
+        <v>118911463</v>
       </c>
       <c r="B4" t="n">
-        <v>97853</v>
+        <v>90476</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,39 +899,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>802668</v>
+        <v>802822</v>
       </c>
       <c r="R4" t="n">
-        <v>7146187</v>
+        <v>7146243</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,11 +970,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-04</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>15 st i blomning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,7 +997,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118912775</v>
+        <v>118913425</v>
       </c>
       <c r="B5" t="n">
         <v>57290</v>
@@ -1055,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>802682</v>
+        <v>802623</v>
       </c>
       <c r="R5" t="n">
-        <v>7146278</v>
+        <v>7146248</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118912069</v>
+        <v>118913514</v>
       </c>
       <c r="B6" t="n">
-        <v>90511</v>
+        <v>78491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,29 +1123,25 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1164,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>802588</v>
+        <v>802618</v>
       </c>
       <c r="R6" t="n">
-        <v>7146291</v>
+        <v>7146315</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,19 +1201,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118912814</v>
+        <v>118913017</v>
       </c>
       <c r="B7" t="n">
         <v>78491</v>
@@ -1262,11 +1248,7 @@
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1274,10 +1256,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>802750</v>
+        <v>802714</v>
       </c>
       <c r="R7" t="n">
-        <v>7146284</v>
+        <v>7146151</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118911374</v>
+        <v>118911495</v>
       </c>
       <c r="B8" t="n">
-        <v>78491</v>
+        <v>82270</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,27 +1335,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1384,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>802668</v>
+        <v>802848</v>
       </c>
       <c r="R8" t="n">
-        <v>7146310</v>
+        <v>7146203</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,7 +1429,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118911854</v>
+        <v>118911768</v>
       </c>
       <c r="B9" t="n">
         <v>97853</v>
@@ -1495,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>802680</v>
+        <v>802693</v>
       </c>
       <c r="R9" t="n">
-        <v>7146179</v>
+        <v>7146165</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118913472</v>
+        <v>118911959</v>
       </c>
       <c r="B10" t="n">
-        <v>90529</v>
+        <v>97853</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1570,30 +1552,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1601,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>802619</v>
+        <v>802668</v>
       </c>
       <c r="R10" t="n">
-        <v>7146280</v>
+        <v>7146187</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1639,6 +1630,11 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>15 st i blomning</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1652,22 +1648,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118912764</v>
+        <v>118911573</v>
       </c>
       <c r="B11" t="n">
-        <v>57290</v>
+        <v>97853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1676,35 +1672,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>802684</v>
+        <v>802695</v>
       </c>
       <c r="R11" t="n">
-        <v>7146282</v>
+        <v>7146163</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,31 +1750,37 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ca 60st i blomning</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118913094</v>
+        <v>118913104</v>
       </c>
       <c r="B12" t="n">
         <v>78491</v>
@@ -1817,10 +1823,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>802616</v>
+        <v>802635</v>
       </c>
       <c r="R12" t="n">
-        <v>7146197</v>
+        <v>7146237</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1880,7 +1886,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118913425</v>
+        <v>118913093</v>
       </c>
       <c r="B13" t="n">
         <v>57290</v>
@@ -1928,10 +1934,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>802623</v>
+        <v>802616</v>
       </c>
       <c r="R13" t="n">
-        <v>7146248</v>
+        <v>7146197</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1964,6 +1970,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1990,10 +2001,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118911445</v>
+        <v>118911927</v>
       </c>
       <c r="B14" t="n">
-        <v>57290</v>
+        <v>57306</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2006,16 +2017,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2038,10 +2049,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>802707</v>
+        <v>802674</v>
       </c>
       <c r="R14" t="n">
-        <v>7146299</v>
+        <v>7146180</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2078,7 +2089,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>äldre påbörjat bohål i gran</t>
+          <t>hack i död gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2105,10 +2116,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118911927</v>
+        <v>118913527</v>
       </c>
       <c r="B15" t="n">
-        <v>57306</v>
+        <v>57290</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2121,16 +2132,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2153,10 +2164,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>802674</v>
+        <v>802655</v>
       </c>
       <c r="R15" t="n">
-        <v>7146180</v>
+        <v>7146316</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2191,11 +2202,6 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>hack i död gran</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2208,19 +2214,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118913514</v>
+        <v>118913543</v>
       </c>
       <c r="B16" t="n">
         <v>78491</v>
@@ -2263,10 +2269,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>802618</v>
+        <v>802655</v>
       </c>
       <c r="R16" t="n">
-        <v>7146315</v>
+        <v>7146316</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2326,10 +2332,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118912823</v>
+        <v>118911433</v>
       </c>
       <c r="B17" t="n">
-        <v>57290</v>
+        <v>78525</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2342,31 +2348,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2374,10 +2379,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>802776</v>
+        <v>802684</v>
       </c>
       <c r="R17" t="n">
-        <v>7146250</v>
+        <v>7146303</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2418,28 +2423,29 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118911573</v>
+        <v>118913436</v>
       </c>
       <c r="B18" t="n">
-        <v>97853</v>
+        <v>57290</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2448,39 +2454,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2488,10 +2490,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>802695</v>
+        <v>802622</v>
       </c>
       <c r="R18" t="n">
-        <v>7146163</v>
+        <v>7146257</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2526,37 +2528,31 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>ca 60st i blomning</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118911768</v>
+        <v>118911854</v>
       </c>
       <c r="B19" t="n">
         <v>97853</v>
@@ -2604,10 +2600,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>802693</v>
+        <v>802680</v>
       </c>
       <c r="R19" t="n">
-        <v>7146165</v>
+        <v>7146179</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2667,10 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118912755</v>
+        <v>118911445</v>
       </c>
       <c r="B20" t="n">
-        <v>78491</v>
+        <v>57290</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2683,26 +2679,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2710,10 +2711,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>802684</v>
+        <v>802707</v>
       </c>
       <c r="R20" t="n">
-        <v>7146282</v>
+        <v>7146299</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2748,32 +2749,36 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>äldre påbörjat bohål i gran</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118912851</v>
+        <v>118912802</v>
       </c>
       <c r="B21" t="n">
         <v>78491</v>
@@ -2808,11 +2813,7 @@
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2820,10 +2821,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>802826</v>
+        <v>802711</v>
       </c>
       <c r="R21" t="n">
-        <v>7146174</v>
+        <v>7146289</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2883,10 +2884,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118913502</v>
+        <v>118912851</v>
       </c>
       <c r="B22" t="n">
-        <v>90854</v>
+        <v>78491</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2895,30 +2896,34 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2926,10 +2931,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>802579</v>
+        <v>802826</v>
       </c>
       <c r="R22" t="n">
-        <v>7146294</v>
+        <v>7146174</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2989,10 +2994,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118911985</v>
+        <v>118911374</v>
       </c>
       <c r="B23" t="n">
-        <v>90476</v>
+        <v>78491</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3001,31 +3006,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -3039,7 +3044,7 @@
         <v>802668</v>
       </c>
       <c r="R23" t="n">
-        <v>7146192</v>
+        <v>7146310</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3099,10 +3104,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118913527</v>
+        <v>118912023</v>
       </c>
       <c r="B24" t="n">
-        <v>57290</v>
+        <v>82270</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3115,31 +3120,30 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3147,10 +3151,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>802655</v>
+        <v>802582</v>
       </c>
       <c r="R24" t="n">
-        <v>7146316</v>
+        <v>7146293</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3191,28 +3195,29 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118913017</v>
+        <v>118912743</v>
       </c>
       <c r="B25" t="n">
-        <v>78491</v>
+        <v>91412</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3225,21 +3230,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>4745</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3252,10 +3257,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>802714</v>
+        <v>802703</v>
       </c>
       <c r="R25" t="n">
-        <v>7146151</v>
+        <v>7146394</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3315,7 +3320,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118912076</v>
+        <v>118911985</v>
       </c>
       <c r="B26" t="n">
         <v>90476</v>
@@ -3362,10 +3367,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>802588</v>
+        <v>802668</v>
       </c>
       <c r="R26" t="n">
-        <v>7146291</v>
+        <v>7146192</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3425,7 +3430,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118912837</v>
+        <v>118912823</v>
       </c>
       <c r="B27" t="n">
         <v>57290</v>
@@ -3473,10 +3478,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>802834</v>
+        <v>802776</v>
       </c>
       <c r="R27" t="n">
-        <v>7146213</v>
+        <v>7146250</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3535,7 +3540,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118912793</v>
+        <v>118912764</v>
       </c>
       <c r="B28" t="n">
         <v>57290</v>
@@ -3583,10 +3588,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>802713</v>
+        <v>802684</v>
       </c>
       <c r="R28" t="n">
-        <v>7146294</v>
+        <v>7146282</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3619,11 +3624,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-08-04</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Påbörjat bohål</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3650,10 +3650,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118911433</v>
+        <v>118913094</v>
       </c>
       <c r="B29" t="n">
-        <v>78525</v>
+        <v>78491</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3666,29 +3666,25 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
@@ -3697,10 +3693,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>802684</v>
+        <v>802616</v>
       </c>
       <c r="R29" t="n">
-        <v>7146303</v>
+        <v>7146197</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3748,22 +3744,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118912023</v>
+        <v>118912069</v>
       </c>
       <c r="B30" t="n">
-        <v>82270</v>
+        <v>90511</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3776,21 +3772,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3807,10 +3803,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>802582</v>
+        <v>802588</v>
       </c>
       <c r="R30" t="n">
-        <v>7146293</v>
+        <v>7146291</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3870,10 +3866,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118911495</v>
+        <v>118912837</v>
       </c>
       <c r="B31" t="n">
-        <v>82270</v>
+        <v>57290</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3886,30 +3882,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3917,10 +3914,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>802848</v>
+        <v>802834</v>
       </c>
       <c r="R31" t="n">
-        <v>7146203</v>
+        <v>7146213</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3961,26 +3958,25 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118913104</v>
+        <v>118912875</v>
       </c>
       <c r="B32" t="n">
         <v>78491</v>
@@ -4023,10 +4019,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>802635</v>
+        <v>802745</v>
       </c>
       <c r="R32" t="n">
-        <v>7146237</v>
+        <v>7146191</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4086,7 +4082,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118911463</v>
+        <v>118912076</v>
       </c>
       <c r="B33" t="n">
         <v>90476</v>
@@ -4133,10 +4129,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>802822</v>
+        <v>802588</v>
       </c>
       <c r="R33" t="n">
-        <v>7146243</v>
+        <v>7146291</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4196,7 +4192,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118912875</v>
+        <v>118912901</v>
       </c>
       <c r="B34" t="n">
         <v>78491</v>
@@ -4239,10 +4235,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>802745</v>
+        <v>802814</v>
       </c>
       <c r="R34" t="n">
-        <v>7146191</v>
+        <v>7146177</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4302,7 +4298,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118913093</v>
+        <v>118912793</v>
       </c>
       <c r="B35" t="n">
         <v>57290</v>
@@ -4350,10 +4346,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>802616</v>
+        <v>802713</v>
       </c>
       <c r="R35" t="n">
-        <v>7146197</v>
+        <v>7146294</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4390,7 +4386,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Påbörjat bohål</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4417,10 +4413,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118912901</v>
+        <v>118912775</v>
       </c>
       <c r="B36" t="n">
-        <v>78491</v>
+        <v>57290</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4433,26 +4429,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4460,10 +4461,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>802814</v>
+        <v>802682</v>
       </c>
       <c r="R36" t="n">
-        <v>7146177</v>
+        <v>7146278</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4504,7 +4505,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4523,10 +4523,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118912743</v>
+        <v>118912814</v>
       </c>
       <c r="B37" t="n">
-        <v>91412</v>
+        <v>78491</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4539,26 +4539,30 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4745</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4566,10 +4570,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>802703</v>
+        <v>802750</v>
       </c>
       <c r="R37" t="n">
-        <v>7146394</v>
+        <v>7146284</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4629,10 +4633,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118913436</v>
+        <v>118913502</v>
       </c>
       <c r="B38" t="n">
-        <v>57290</v>
+        <v>90854</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4641,35 +4645,30 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4677,10 +4676,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>802622</v>
+        <v>802579</v>
       </c>
       <c r="R38" t="n">
-        <v>7146257</v>
+        <v>7146294</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4721,6 +4720,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9162-2024 artfynd.xlsx
+++ b/artfynd/A 9162-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118912775</v>
+        <v>118911433</v>
       </c>
       <c r="B2" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,31 +686,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>802682</v>
+        <v>802684</v>
       </c>
       <c r="R2" t="n">
-        <v>7146278</v>
+        <v>7146303</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -767,33 +761,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118912793</v>
+        <v>118912069</v>
       </c>
       <c r="B3" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,31 +791,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>802713</v>
+        <v>802588</v>
       </c>
       <c r="R3" t="n">
-        <v>7146294</v>
+        <v>7146291</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,44 +860,35 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påbörjat bohål</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118913104</v>
+        <v>118911495</v>
       </c>
       <c r="B4" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,25 +896,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -943,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>802635</v>
+        <v>802848</v>
       </c>
       <c r="R4" t="n">
-        <v>7146237</v>
+        <v>7146203</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,27 +978,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118913017</v>
+        <v>118912023</v>
       </c>
       <c r="B5" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,25 +1001,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1049,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>802714</v>
+        <v>802582</v>
       </c>
       <c r="R5" t="n">
-        <v>7146151</v>
+        <v>7146293</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,49 +1083,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118912875</v>
+        <v>118913502</v>
       </c>
       <c r="B6" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92281</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1155,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>802745</v>
+        <v>802579</v>
       </c>
       <c r="R6" t="n">
-        <v>7146191</v>
+        <v>7146294</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,15 +1196,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118911433</v>
+        <v>118912743</v>
       </c>
       <c r="B7" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1234,29 +1207,25 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>4745</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1265,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>802684</v>
+        <v>802703</v>
       </c>
       <c r="R7" t="n">
-        <v>7146303</v>
+        <v>7146394</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,53 +1285,52 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118913472</v>
+        <v>118911463</v>
       </c>
       <c r="B8" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1371,10 +1339,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>802619</v>
+        <v>802822</v>
       </c>
       <c r="R8" t="n">
-        <v>7146280</v>
+        <v>7146243</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,59 +1390,53 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118913436</v>
+        <v>118911503</v>
       </c>
       <c r="B9" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1482,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>802622</v>
+        <v>802815</v>
       </c>
       <c r="R9" t="n">
-        <v>7146257</v>
+        <v>7146163</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,65 +1488,60 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118912837</v>
+        <v>118911985</v>
       </c>
       <c r="B10" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1592,10 +1549,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>802834</v>
+        <v>802668</v>
       </c>
       <c r="R10" t="n">
-        <v>7146213</v>
+        <v>7146192</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1636,65 +1593,60 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118913093</v>
+        <v>118912076</v>
       </c>
       <c r="B11" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1702,10 +1654,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>802616</v>
+        <v>802588</v>
       </c>
       <c r="R11" t="n">
-        <v>7146197</v>
+        <v>7146291</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,76 +1692,66 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118912823</v>
+        <v>118911374</v>
       </c>
       <c r="B12" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1817,10 +1759,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>802776</v>
+        <v>802668</v>
       </c>
       <c r="R12" t="n">
-        <v>7146250</v>
+        <v>7146310</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1861,65 +1803,56 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118911445</v>
+        <v>118912728</v>
       </c>
       <c r="B13" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1927,10 +1860,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>802707</v>
+        <v>802559</v>
       </c>
       <c r="R13" t="n">
-        <v>7146299</v>
+        <v>7146892</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,76 +1898,62 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>äldre påbörjat bohål i gran</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118911927</v>
+        <v>118912755</v>
       </c>
       <c r="B14" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2042,10 +1961,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>802674</v>
+        <v>802684</v>
       </c>
       <c r="R14" t="n">
-        <v>7146180</v>
+        <v>7146282</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2080,76 +1999,62 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>hack i död gran</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118913527</v>
+        <v>118912802</v>
       </c>
       <c r="B15" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2157,10 +2062,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>802655</v>
+        <v>802711</v>
       </c>
       <c r="R15" t="n">
-        <v>7146316</v>
+        <v>7146289</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2201,6 +2106,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2219,45 +2125,39 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118912764</v>
+        <v>118912814</v>
       </c>
       <c r="B16" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2267,10 +2167,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>802684</v>
+        <v>802750</v>
       </c>
       <c r="R16" t="n">
-        <v>7146282</v>
+        <v>7146284</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2311,6 +2211,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2329,19 +2230,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118912901</v>
+        <v>118912851</v>
       </c>
       <c r="B17" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2364,7 +2260,11 @@
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2372,10 +2272,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>802814</v>
+        <v>802826</v>
       </c>
       <c r="R17" t="n">
-        <v>7146177</v>
+        <v>7146174</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2435,15 +2335,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118913502</v>
+        <v>118912875</v>
       </c>
       <c r="B18" t="n">
-        <v>90856</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2451,21 +2346,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2478,10 +2373,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>802579</v>
+        <v>802745</v>
       </c>
       <c r="R18" t="n">
-        <v>7146294</v>
+        <v>7146191</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2541,15 +2436,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118911854</v>
+        <v>118912901</v>
       </c>
       <c r="B19" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2557,31 +2447,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2589,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>802680</v>
+        <v>802814</v>
       </c>
       <c r="R19" t="n">
-        <v>7146179</v>
+        <v>7146177</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2640,31 +2525,26 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118912755</v>
+        <v>118913017</v>
       </c>
       <c r="B20" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2695,10 +2575,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>802684</v>
+        <v>802714</v>
       </c>
       <c r="R20" t="n">
-        <v>7146282</v>
+        <v>7146151</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2758,19 +2638,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118912802</v>
+        <v>118913094</v>
       </c>
       <c r="B21" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2801,10 +2676,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>802711</v>
+        <v>802616</v>
       </c>
       <c r="R21" t="n">
-        <v>7146289</v>
+        <v>7146197</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2864,45 +2739,36 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118911463</v>
+        <v>118913104</v>
       </c>
       <c r="B22" t="n">
-        <v>90478</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -2911,10 +2777,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>802822</v>
+        <v>802635</v>
       </c>
       <c r="R22" t="n">
-        <v>7146243</v>
+        <v>7146237</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2962,31 +2828,26 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118913094</v>
+        <v>118913514</v>
       </c>
       <c r="B23" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3017,10 +2878,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>802616</v>
+        <v>802618</v>
       </c>
       <c r="R23" t="n">
-        <v>7146197</v>
+        <v>7146315</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3080,15 +2941,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118911768</v>
+        <v>118913543</v>
       </c>
       <c r="B24" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3096,31 +2952,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3128,10 +2979,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>802693</v>
+        <v>802655</v>
       </c>
       <c r="R24" t="n">
-        <v>7146165</v>
+        <v>7146316</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3179,58 +3030,54 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118912069</v>
+        <v>118911927</v>
       </c>
       <c r="B25" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3238,10 +3085,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>802588</v>
+        <v>802674</v>
       </c>
       <c r="R25" t="n">
-        <v>7146291</v>
+        <v>7146180</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3276,13 +3123,17 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>hack i död gran</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3301,15 +3152,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118912814</v>
+        <v>118911445</v>
       </c>
       <c r="B26" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3317,28 +3163,29 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3348,10 +3195,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>802750</v>
+        <v>802707</v>
       </c>
       <c r="R26" t="n">
-        <v>7146284</v>
+        <v>7146299</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3386,71 +3233,71 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>äldre påbörjat bohål i gran</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118911985</v>
+        <v>118912764</v>
       </c>
       <c r="B27" t="n">
-        <v>90478</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3458,10 +3305,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>802668</v>
+        <v>802684</v>
       </c>
       <c r="R27" t="n">
-        <v>7146192</v>
+        <v>7146282</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3502,34 +3349,28 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118912851</v>
+        <v>118912775</v>
       </c>
       <c r="B28" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3537,28 +3378,29 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3568,10 +3410,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>802826</v>
+        <v>802682</v>
       </c>
       <c r="R28" t="n">
-        <v>7146174</v>
+        <v>7146278</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3612,7 +3454,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3631,15 +3472,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118912743</v>
+        <v>118912793</v>
       </c>
       <c r="B29" t="n">
-        <v>91414</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3647,26 +3483,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4745</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3674,10 +3515,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>802703</v>
+        <v>802713</v>
       </c>
       <c r="R29" t="n">
-        <v>7146394</v>
+        <v>7146294</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3712,13 +3553,17 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Påbörjat bohål</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3737,51 +3582,42 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118911573</v>
+        <v>118912823</v>
       </c>
       <c r="B30" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3789,10 +3625,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>802695</v>
+        <v>802776</v>
       </c>
       <c r="R30" t="n">
-        <v>7146163</v>
+        <v>7146250</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3827,81 +3663,66 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>ca 60st i blomning</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118911959</v>
+        <v>118912837</v>
       </c>
       <c r="B31" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3909,10 +3730,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>802668</v>
+        <v>802834</v>
       </c>
       <c r="R31" t="n">
-        <v>7146187</v>
+        <v>7146213</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3947,45 +3768,34 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>15 st i blomning</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118911374</v>
+        <v>118913093</v>
       </c>
       <c r="B32" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3993,30 +3803,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4024,10 +3835,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>802668</v>
+        <v>802616</v>
       </c>
       <c r="R32" t="n">
-        <v>7146310</v>
+        <v>7146197</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4062,40 +3873,39 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118913543</v>
+        <v>118913425</v>
       </c>
       <c r="B33" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4103,26 +3913,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4130,10 +3945,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>802655</v>
+        <v>802623</v>
       </c>
       <c r="R33" t="n">
-        <v>7146316</v>
+        <v>7146248</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4174,7 +3989,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4193,15 +4007,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118911495</v>
+        <v>118913436</v>
       </c>
       <c r="B34" t="n">
-        <v>82272</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4209,30 +4018,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4240,10 +4050,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>802848</v>
+        <v>802622</v>
       </c>
       <c r="R34" t="n">
-        <v>7146203</v>
+        <v>7146257</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4284,34 +4094,28 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118913425</v>
+        <v>118913527</v>
       </c>
       <c r="B35" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4351,10 +4155,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>802623</v>
+        <v>802655</v>
       </c>
       <c r="R35" t="n">
-        <v>7146248</v>
+        <v>7146316</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4413,46 +4217,46 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118912076</v>
+        <v>118911573</v>
       </c>
       <c r="B36" t="n">
-        <v>90478</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4460,10 +4264,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>802588</v>
+        <v>802695</v>
       </c>
       <c r="R36" t="n">
-        <v>7146291</v>
+        <v>7146163</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4496,6 +4300,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>ca 60st i blomning</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4523,46 +4332,42 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118912023</v>
+        <v>118911768</v>
       </c>
       <c r="B37" t="n">
-        <v>82272</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4570,10 +4375,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>802582</v>
+        <v>802693</v>
       </c>
       <c r="R37" t="n">
-        <v>7146293</v>
+        <v>7146165</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4633,42 +4438,42 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118913514</v>
+        <v>118911854</v>
       </c>
       <c r="B38" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4676,10 +4481,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>802618</v>
+        <v>802680</v>
       </c>
       <c r="R38" t="n">
-        <v>7146315</v>
+        <v>7146179</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4727,15 +4532,130 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>118911959</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Pottermyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>802668</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7146187</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>15 st i blomning</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9162-2024 artfynd.xlsx
+++ b/artfynd/A 9162-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118911433</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118912069</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118911495</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118912023</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1193,6 +1218,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118913502</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118912743</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1399,6 +1434,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118911463</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1504,6 +1544,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118911503</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1609,6 +1654,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118911985</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1714,6 +1764,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118912076</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1819,6 +1874,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118911374</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1920,6 +1980,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118912728</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2021,6 +2086,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118912755</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2122,6 +2192,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118912802</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2227,6 +2302,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118912814</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2332,6 +2412,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118912851</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2433,6 +2518,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118912875</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2534,6 +2624,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118912901</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2635,6 +2730,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118913017</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2736,6 +2836,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118913094</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2837,6 +2942,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118913104</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2938,6 +3048,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118913514</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3039,6 +3154,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118913543</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3149,6 +3269,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118911927</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3259,6 +3384,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118911445</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3364,6 +3494,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118912764</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3469,6 +3604,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118912775</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3579,6 +3719,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118912793</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3684,6 +3829,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118912823</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3789,6 +3939,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118912837</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3899,6 +4054,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118913093</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4004,6 +4164,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118913425</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4109,6 +4274,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118913436</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4214,6 +4384,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118913527</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4329,6 +4504,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118911573</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4435,6 +4615,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118911768</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4541,6 +4726,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118911854</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4656,8 +4846,53 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118911959</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>